--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.41947236824066</v>
+        <v>6.568164259839108</v>
       </c>
       <c r="D2" t="n">
-        <v>40.72920490557441</v>
+        <v>6.618495797155841</v>
       </c>
       <c r="E2" t="n">
-        <v>5.868850971527575</v>
+        <v>0.9536882828732309</v>
       </c>
       <c r="F2" t="n">
-        <v>6.073049963725876</v>
+        <v>0.9868706191054548</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.38652677119172</v>
+        <v>4.775310600318655</v>
       </c>
       <c r="D3" t="n">
-        <v>29.80198035751736</v>
+        <v>4.842821808096571</v>
       </c>
       <c r="E3" t="n">
-        <v>5.868850971527575</v>
+        <v>0.9536882828732309</v>
       </c>
       <c r="F3" t="n">
-        <v>6.073049963725876</v>
+        <v>0.9868706191054548</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.04951261329526</v>
+        <v>4.233045799660481</v>
       </c>
       <c r="D4" t="n">
-        <v>25.66394779235071</v>
+        <v>4.17039151625699</v>
       </c>
       <c r="E4" t="n">
-        <v>5.868850971527575</v>
+        <v>0.9536882828732309</v>
       </c>
       <c r="F4" t="n">
-        <v>6.073049963725876</v>
+        <v>0.9868706191054548</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.49824645561881</v>
+        <v>3.980965049038057</v>
       </c>
       <c r="D5" t="n">
-        <v>24.06027077216444</v>
+        <v>3.909794000476721</v>
       </c>
       <c r="E5" t="n">
-        <v>5.868850971527575</v>
+        <v>0.9536882828732309</v>
       </c>
       <c r="F5" t="n">
-        <v>6.073049963725876</v>
+        <v>0.9868706191054548</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.75627475120121</v>
+        <v>5.647894647070197</v>
       </c>
       <c r="D6" t="n">
-        <v>34.42120183734907</v>
+        <v>5.593445298569224</v>
       </c>
       <c r="E6" t="n">
-        <v>5.868850971527575</v>
+        <v>0.9536882828732309</v>
       </c>
       <c r="F6" t="n">
-        <v>6.073049963725876</v>
+        <v>0.9868706191054548</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
